--- a/data/li-ion_module_samples/module_list.xlsx
+++ b/data/li-ion_module_samples/module_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lnkassa/batteryarchive-agent/data/li-ion module samples/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lnkassa/batteryarchive-agent/data/li-ion_module_samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245FF4E4-C572-A64D-96F1-327944D8D626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E057103F-825D-F249-BCA4-EF91A6CB14B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29200" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{07EF3D65-9BA3-43DB-B014-0F8C59FBB292}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15320" xr2:uid="{07EF3D65-9BA3-43DB-B014-0F8C59FBB292}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>module_id</t>
   </si>
   <si>
-    <t>Configuration</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>SNL_8S-1P_NMC_25C_20-80_0.5/0.5C</t>
+  </si>
+  <si>
+    <t>configuration</t>
   </si>
 </sst>
 </file>
@@ -506,13 +506,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -559,10 +559,10 @@
         <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2">
         <v>8</v>
